--- a/data/trans_orig/IP19C01-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP19C01-Edad-trans_orig.xlsx
@@ -733,7 +733,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2711</t>
+          <t>2633</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2904</t>
+          <t>2809</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3088</t>
+          <t>3166</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>54,6%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64431</t>
+          <t>64600</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75476</t>
+          <t>76138</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62274</t>
+          <t>62637</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72352</t>
+          <t>72886</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>130092</t>
+          <t>130653</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>145905</t>
+          <t>145560</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,35%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8859</t>
+          <t>8197</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19904</t>
+          <t>19735</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8066</t>
+          <t>7532</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18144</t>
+          <t>17781</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>18848</t>
+          <t>19193</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>34661</t>
+          <t>34100</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,7%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>61710</t>
+          <t>62092</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>76867</t>
+          <t>76654</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>77706</t>
+          <t>77672</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>91181</t>
+          <t>91205</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>144380</t>
+          <t>144642</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>163939</t>
+          <t>164702</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>80,38%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22326</t>
+          <t>22539</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37483</t>
+          <t>37101</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14538</t>
+          <t>14514</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28013</t>
+          <t>28047</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>40973</t>
+          <t>40210</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>60532</t>
+          <t>60270</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,41%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>78205</t>
+          <t>78028</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>98439</t>
+          <t>98472</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>92322</t>
+          <t>92968</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>114052</t>
+          <t>112563</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>176568</t>
+          <t>177345</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>206475</t>
+          <t>206609</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>61,27%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>65058</t>
+          <t>65025</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>85292</t>
+          <t>85469</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>52,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>59649</t>
+          <t>61138</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>81379</t>
+          <t>80733</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>130722</t>
+          <t>130588</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>160629</t>
+          <t>159852</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>47,41%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>217367</t>
+          <t>216587</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>245325</t>
+          <t>244928</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>244823</t>
+          <t>244598</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>271292</t>
+          <t>271064</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>67,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>470225</t>
+          <t>470844</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>511548</t>
+          <t>509320</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,47%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>105605</t>
+          <t>106002</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>133563</t>
+          <t>134343</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>90439</t>
+          <t>90667</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>116908</t>
+          <t>117133</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>201113</t>
+          <t>203341</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>242436</t>
+          <t>241817</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>33,93%</t>
         </is>
       </c>
     </row>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>692</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3228</t>
+          <t>3275</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>82,55%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55612</t>
+          <t>55098</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67870</t>
+          <t>67397</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>67771</t>
+          <t>67839</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>81202</t>
+          <t>80548</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>73,12%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>128544</t>
+          <t>128319</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>145870</t>
+          <t>145547</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>84,79%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11112</t>
+          <t>11585</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23370</t>
+          <t>23884</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11477</t>
+          <t>12131</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24908</t>
+          <t>24840</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>25791</t>
+          <t>26114</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>43117</t>
+          <t>43342</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,25%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>85565</t>
+          <t>85409</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>101432</t>
+          <t>101782</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>86203</t>
+          <t>87296</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>103453</t>
+          <t>103869</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>178554</t>
+          <t>178715</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>201243</t>
+          <t>201362</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>78,08%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24390</t>
+          <t>24040</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40257</t>
+          <t>40413</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28633</t>
+          <t>28217</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45883</t>
+          <t>44790</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>56665</t>
+          <t>56546</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>79354</t>
+          <t>79193</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,71%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88995</t>
+          <t>87622</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>107383</t>
+          <t>106473</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>98246</t>
+          <t>98719</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>114375</t>
+          <t>115056</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>192186</t>
+          <t>190982</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>217291</t>
+          <t>217367</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>74,98%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>40537</t>
+          <t>41447</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>58925</t>
+          <t>60298</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27588</t>
+          <t>26907</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43717</t>
+          <t>43244</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>72591</t>
+          <t>72515</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>97696</t>
+          <t>98900</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>34,12%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>243057</t>
+          <t>243040</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>269024</t>
+          <t>270963</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>264985</t>
+          <t>264906</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>292453</t>
+          <t>292529</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>516222</t>
+          <t>516752</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>555101</t>
+          <t>553917</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,57%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>86997</t>
+          <t>85058</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>112964</t>
+          <t>112981</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>74944</t>
+          <t>74868</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>102412</t>
+          <t>102491</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>168317</t>
+          <t>169501</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>207196</t>
+          <t>206666</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,57%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>49406</t>
+          <t>49422</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60188</t>
+          <t>60158</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59608</t>
+          <t>59850</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>71842</t>
+          <t>71772</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>112904</t>
+          <t>112270</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>128698</t>
+          <t>128648</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,89%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8596</t>
+          <t>8626</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19378</t>
+          <t>19362</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10920</t>
+          <t>10990</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23154</t>
+          <t>22912</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>22848</t>
+          <t>22898</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>38642</t>
+          <t>39276</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,92%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>101791</t>
+          <t>102195</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>119298</t>
+          <t>119413</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>68,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>109086</t>
+          <t>110932</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>126537</t>
+          <t>126977</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>218221</t>
+          <t>217695</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>241900</t>
+          <t>242829</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,83%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30522</t>
+          <t>30407</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48029</t>
+          <t>47625</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24050</t>
+          <t>23610</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41501</t>
+          <t>39655</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>58507</t>
+          <t>57578</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>82186</t>
+          <t>82712</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,53%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>91263</t>
+          <t>91809</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>110126</t>
+          <t>110726</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>85828</t>
+          <t>86788</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>103876</t>
+          <t>104704</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>63,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>210565</t>
+          <t>208515</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>73,77%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>35757</t>
+          <t>35157</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>54620</t>
+          <t>54074</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>32893</t>
+          <t>32065</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>50941</t>
+          <t>49981</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>72087</t>
+          <t>74137</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>253328</t>
+          <t>254511</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>282120</t>
+          <t>283010</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>267518</t>
+          <t>268115</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>294469</t>
+          <t>294193</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>529969</t>
+          <t>530285</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>569772</t>
+          <t>568634</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>77,22%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>82904</t>
+          <t>82014</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>111696</t>
+          <t>110513</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>76933</t>
+          <t>77209</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>103884</t>
+          <t>103287</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>166653</t>
+          <t>167791</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>206456</t>
+          <t>206140</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,99%</t>
         </is>
       </c>
     </row>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>2075</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -6589,7 +6589,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -6609,7 +6609,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>1939</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -6624,7 +6624,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5549</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10327</t>
+          <t>10339</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>93,04%</t>
         </is>
       </c>
     </row>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4061</t>
+          <t>3722</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>64,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6727,7 +6727,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3413</t>
+          <t>3382</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>774</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>5715</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>51,43%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>49483</t>
+          <t>50024</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59652</t>
+          <t>59683</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>75,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58664</t>
+          <t>58199</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70148</t>
+          <t>70243</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>111944</t>
+          <t>112179</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>127427</t>
+          <t>127215</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,76%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6544</t>
+          <t>6513</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16713</t>
+          <t>16172</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6983</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18467</t>
+          <t>18932</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15900</t>
+          <t>16112</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>31383</t>
+          <t>31148</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,73%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>89315</t>
+          <t>88516</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>106865</t>
+          <t>107254</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,49 +7275,49 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>87,98%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>135743</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>125941</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>144446</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>82,37%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>76,43%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
           <t>87,66%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>135743</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>125955</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>143825</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>82,37%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>76,43%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>87,28%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>290</t>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>220916</t>
+          <t>221879</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>247442</t>
+          <t>247117</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,2%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15038</t>
+          <t>14649</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32588</t>
+          <t>33387</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,44 +7388,44 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>12,02%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>27,39%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>29045</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>20342</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>38847</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>17,63%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
           <t>12,34%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>26,73%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>29045</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>20963</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>38833</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>17,63%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>12,72%</t>
-        </is>
-      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
           <t>23,57%</t>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>39249</t>
+          <t>39574</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>65775</t>
+          <t>64812</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,61%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>150298</t>
+          <t>149628</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>169673</t>
+          <t>169036</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>180584</t>
+          <t>179550</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>206054</t>
+          <t>206090</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>336940</t>
+          <t>338488</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>369641</t>
+          <t>371500</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>85,41%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28064</t>
+          <t>28701</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>47439</t>
+          <t>48109</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>31154</t>
+          <t>31118</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>56624</t>
+          <t>57658</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>65304</t>
+          <t>63445</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>98005</t>
+          <t>96457</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,18%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>305727</t>
+          <t>304341</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>332886</t>
+          <t>332207</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>379470</t>
+          <t>381145</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>414420</t>
+          <t>414784</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>694445</t>
+          <t>696742</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>738683</t>
+          <t>739765</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,44%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>58747</t>
+          <t>59426</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>85906</t>
+          <t>87292</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>70024</t>
+          <t>69660</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>104974</t>
+          <t>103299</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>137393</t>
+          <t>136311</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>181631</t>
+          <t>179334</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,47%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP19C01-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP19C01-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,74 +723,74 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1893</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>3138</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1097</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>898</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>3906</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>80,33%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>28,09%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>22,98%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1893</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>8</t>
@@ -803,7 +803,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2633</t>
+          <t>2389</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -836,107 +836,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>768</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2809</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>19,67%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>71,91%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>77,02%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>3410</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>13,25%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>3166</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>13,25%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>58,81%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1893</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1893</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1893</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>3906</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>3906</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>3906</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1893</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1893</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1893</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>67975</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>62182</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>72618</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>84,53%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>77,32%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>90,3%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>70788</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>64600</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>76138</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>64545</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>76069</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>83,94%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>76,6%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>90,28%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>67975</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>62637</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>72886</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>84,53%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>130653</t>
+          <t>130656</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>145560</t>
+          <t>146275</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,78%</t>
         </is>
       </c>
     </row>
@@ -1184,67 +1184,67 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>12443</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7800</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>18236</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>15,47%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>9,7%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>22,68%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>13547</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>8197</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>19735</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>8266</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>19790</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>16,06%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,72%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>23,4%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>12443</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>7532</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>17781</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>15,47%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>19193</t>
+          <t>18478</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>34100</t>
+          <t>34097</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>80418</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>80418</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>80418</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>84335</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>84335</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>84335</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>80418</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>80418</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>80418</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>84978</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>77715</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>90833</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>80,38%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>73,51%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>85,92%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>69875</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>62092</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>76654</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>62646</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>77199</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>70,44%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>62,6%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>77,28%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>84978</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>77672</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>91205</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>80,38%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>144642</t>
+          <t>145035</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>164702</t>
+          <t>163860</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>79,97%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>20741</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>14886</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>28004</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>19,62%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>14,08%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>26,49%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>29318</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>22539</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>37101</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>21994</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>36547</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>29,56%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>22,72%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>37,4%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>20741</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>14514</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>28047</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>19,62%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>40210</t>
+          <t>41052</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>60270</t>
+          <t>59877</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,22%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>105719</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>105719</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>105719</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>148</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>99193</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>99193</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>99193</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>105719</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>105719</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>105719</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>103374</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>93823</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>113931</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>59,51%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>54,01%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>65,59%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>88418</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>78028</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>98472</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>78614</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>98978</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>54,08%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>47,72%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>60,23%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>103374</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>92968</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>112563</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>59,51%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>177345</t>
+          <t>177551</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>206609</t>
+          <t>206646</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>61,28%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>59770</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>79878</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>40,49%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>34,41%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>45,99%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>75079</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>65025</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>85469</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>64519</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>84883</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>45,92%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>39,77%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>52,28%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>61138</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>80733</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>40,49%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>130588</t>
+          <t>130551</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>159852</t>
+          <t>159646</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>47,34%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>173701</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>173701</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>173701</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>163497</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>163497</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>163497</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>173701</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>173701</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>173701</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>258220</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>244477</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>272001</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>71,38%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>67,59%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>75,19%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>349</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>232218</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>216587</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>244928</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>215484</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>244818</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>66,17%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>61,72%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>69,79%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>390</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>258220</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>244598</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>271064</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>71,38%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>470844</t>
+          <t>469582</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>509320</t>
+          <t>510472</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>71,63%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>103511</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>89730</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>117254</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>28,62%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>24,81%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>32,41%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>173</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>118712</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>106002</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>134343</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>106112</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>135446</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>33,83%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>30,21%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>38,28%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>103511</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>90667</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>117133</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>28,62%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>203341</t>
+          <t>202189</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>241817</t>
+          <t>243079</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>34,11%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>522</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,74 +2670,74 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2049</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>661</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>3298</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>62,14%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>20,04%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>20,07%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>4</t>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>700</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -2783,107 +2783,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>1249</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2637</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2636</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>37,86%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>79,96%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>79,93%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>1249</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>3267</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>31,48%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1249</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>3275</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>31,48%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,34%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>3298</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>3298</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>3298</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>75349</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>68894</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>80914</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>81,3%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>74,34%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>87,31%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>62049</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>55098</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>67397</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>55335</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>67512</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>78,56%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>69,76%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>85,33%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>75349</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>67839</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>80548</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>81,3%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>128319</t>
+          <t>127523</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>145547</t>
+          <t>145522</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>84,77%</t>
         </is>
       </c>
     </row>
@@ -3131,67 +3131,67 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>17330</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11765</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>23785</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>18,7%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>12,69%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>25,66%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>16933</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>11585</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>23884</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>11470</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>23647</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>21,44%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>14,67%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>30,24%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>17330</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>12131</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>24840</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>18,7%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>26114</t>
+          <t>26139</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>43342</t>
+          <t>44138</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,71%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>92679</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>92679</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>92679</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>78982</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>78982</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>78982</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>92679</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>92679</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>92679</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>96269</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>88011</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>103671</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>72,88%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>66,63%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>78,49%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>94226</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>85409</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>101782</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>86046</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>101371</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>74,89%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>67,88%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>80,89%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>96269</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>87296</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>103869</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>72,88%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>178715</t>
+          <t>178156</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>201362</t>
+          <t>201323</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>78,06%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>35817</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>28415</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>44075</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>27,12%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>21,51%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>33,37%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>31596</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>24040</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>40413</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>24451</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>39776</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>25,11%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>19,11%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>32,12%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>35817</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>28217</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>44790</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>27,12%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>56546</t>
+          <t>56585</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>79193</t>
+          <t>79752</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,92%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>132086</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>132086</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>132086</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>179</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>125822</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>125822</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>125822</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>132086</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>132086</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>132086</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>106845</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>98189</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>114494</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>75,26%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>69,17%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>80,65%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>139</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>98469</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>87622</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>106473</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>89572</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>108234</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>66,57%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>59,24%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>71,98%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>106845</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>98719</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>115056</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>75,26%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>190982</t>
+          <t>192765</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>217367</t>
+          <t>217585</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>75,06%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>35118</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>27469</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>43774</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>24,74%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>19,35%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>30,83%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>49451</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>41447</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>60298</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>39686</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>58348</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>33,43%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>28,02%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>40,76%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>35118</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>26907</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>43244</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>24,74%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>72515</t>
+          <t>72297</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>98900</t>
+          <t>97117</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>33,5%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>141963</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>141963</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>141963</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>147920</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>147920</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>147920</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>141963</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>141963</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>141963</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>279132</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>264423</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>291726</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>75,98%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>71,97%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>79,4%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>363</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>256792</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>243040</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>270963</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>241589</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>269703</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>72,13%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>68,27%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>76,11%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>397</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>279132</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>264906</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>292529</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>75,98%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>75,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>516752</t>
+          <t>516958</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>553917</t>
+          <t>554768</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>76,69%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>88265</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>75671</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>102974</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>24,02%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>20,6%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>28,03%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>99229</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>85058</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>112981</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>86318</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>114432</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>27,87%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>23,89%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>31,73%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>88265</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>74868</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>102491</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>24,02%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>169501</t>
+          <t>168650</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>206666</t>
+          <t>206460</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,54%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>526</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>367397</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>367397</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>367397</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>507</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>356021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>356021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>356021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>526</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>367397</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>367397</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>367397</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,47 +4617,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>536</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>536</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>536</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>536</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,74 +4960,74 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>66185</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>59476</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>71872</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>79,97%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>71,86%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>86,84%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>55310</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>49422</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>60158</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>49111</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>60156</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>80,41%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>71,85%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>71,4%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>87,46%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>66185</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>59850</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>71772</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>79,97%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>72,32%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>86,72%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>181</t>
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>112270</t>
+          <t>113572</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>128648</t>
+          <t>129578</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>85,5%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>16577</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>10890</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>23286</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>20,03%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>13,16%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>28,14%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>13474</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>8626</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>19362</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>8628</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>19673</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>19,59%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>12,54%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>28,15%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>16577</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>10990</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>22912</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>20,03%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>13,28%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>22898</t>
+          <t>21968</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>39276</t>
+          <t>37974</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,06%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>82762</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>82762</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>82762</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>68784</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>68784</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>68784</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>82762</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>82762</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>82762</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>119023</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>110105</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>126811</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>79,04%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>73,12%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>84,21%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>158</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>111270</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>102195</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>119413</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>101523</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>119630</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>74,27%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>68,21%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>79,7%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>119023</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>110932</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>126977</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>79,04%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>217695</t>
+          <t>218558</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>242829</t>
+          <t>242670</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,78%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>31564</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>23776</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>40482</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>20,96%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>15,79%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>26,88%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>38550</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>30407</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>47625</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>30190</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>48297</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>25,73%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>20,3%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>31,79%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>31564</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>23610</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>39655</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>20,96%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>57578</t>
+          <t>57737</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>82712</t>
+          <t>81849</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,25%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>150587</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>150587</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>150587</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>149820</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>149820</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>149820</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>150587</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>150587</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>150587</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>95481</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>86323</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>104132</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>69,81%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>63,12%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>76,14%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>142</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>101452</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>91809</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>110726</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>92138</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>110355</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>69,54%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>62,93%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>75,9%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>95481</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>86788</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>104704</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>69,81%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>182902</t>
+          <t>183976</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>208515</t>
+          <t>209650</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>74,17%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>41288</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>32637</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>50446</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>30,19%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>23,86%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>36,88%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>44431</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>35157</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>54074</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>35528</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>53745</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>30,46%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>24,1%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>37,07%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>41288</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>32065</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>49981</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>30,19%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>74137</t>
+          <t>73002</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>99750</t>
+          <t>98676</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>34,91%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>136769</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>136769</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>136769</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>145883</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>145883</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>145883</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>136769</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>136769</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>136769</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>281974</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>268126</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>295931</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>75,92%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>72,19%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>79,68%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>386</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>268568</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>254511</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>283010</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>254062</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>282940</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>73,58%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>69,72%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>77,53%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>388</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>281974</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>268115</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>294193</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>75,92%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>530285</t>
+          <t>530895</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>568634</t>
+          <t>569710</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>77,36%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>89428</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>75471</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>103276</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>24,08%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>20,32%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>27,81%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>96456</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>82014</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>110513</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>82084</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>110962</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>26,42%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>22,47%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>30,28%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>89428</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>77209</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>103287</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>24,08%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>167791</t>
+          <t>166715</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>206140</t>
+          <t>205530</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,91%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>515</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>371402</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>371402</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>371402</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>530</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>365024</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>365024</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>365024</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>515</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>371402</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>371402</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>371402</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,74 +6564,74 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3610</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4676</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>77,21%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>38,49%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4171</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2075</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5797</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>71,95%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>35,8%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>4618</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2440</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6072</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>76,05%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>40,18%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3988</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1939</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5316</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>75,02%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>36,47%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>15</t>
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>8159</t>
+          <t>8228</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5602</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10339</t>
+          <t>10011</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>76,55%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,14%</t>
         </is>
       </c>
     </row>
@@ -6682,7 +6682,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1626</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3722</t>
+          <t>2877</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>61,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1454</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3382</t>
+          <t>3632</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>2954</t>
+          <t>2520</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>737</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>5146</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>47,88%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4676</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4676</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4676</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>5797</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5797</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5797</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5316</t>
+          <t>6072</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5316</t>
+          <t>6072</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5316</t>
+          <t>6072</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>11113</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11113</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11113</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>57238</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>50976</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>61282</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>84,71%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>75,44%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>90,69%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>55323</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>50024</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>59683</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>83,57%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>75,57%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>90,16%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>65166</t>
+          <t>52397</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58199</t>
+          <t>46351</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70243</t>
+          <t>56898</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>120489</t>
+          <t>109636</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>112179</t>
+          <t>102213</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>127215</t>
+          <t>116364</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,81%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>10332</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6288</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>16594</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>15,29%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>9,31%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>24,56%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>10873</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6513</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>16172</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>16,43%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,84%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>24,43%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>11965</t>
+          <t>11052</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>6551</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18932</t>
+          <t>17098</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>22838</t>
+          <t>21384</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16112</t>
+          <t>14656</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>31148</t>
+          <t>28807</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,99%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>67570</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>67570</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>67570</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>66196</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>66196</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>66196</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>77131</t>
+          <t>63449</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>77131</t>
+          <t>63449</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>77131</t>
+          <t>63449</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>143327</t>
+          <t>131020</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>143327</t>
+          <t>131020</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>143327</t>
+          <t>131020</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>127756</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>117301</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>135931</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>82,27%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>75,53%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>87,53%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>99990</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>88516</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>107254</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>82,02%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>72,61%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>87,98%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>135743</t>
+          <t>101825</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>125941</t>
+          <t>93738</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>144446</t>
+          <t>108363</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>235733</t>
+          <t>229582</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>221879</t>
+          <t>217737</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>247117</t>
+          <t>240120</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,64%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>27542</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>19367</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>37997</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>17,73%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>12,47%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>24,47%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>21913</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>14649</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>33387</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>17,98%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>12,02%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>27,39%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>29045</t>
+          <t>20015</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20342</t>
+          <t>13477</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38847</t>
+          <t>28102</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>50958</t>
+          <t>47556</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>39574</t>
+          <t>37018</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>64812</t>
+          <t>59401</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>21,43%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>155298</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>155298</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>155298</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>121903</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>121903</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>121903</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>164788</t>
+          <t>121840</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>164788</t>
+          <t>121840</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>164788</t>
+          <t>121840</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>286691</t>
+          <t>277138</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>286691</t>
+          <t>277138</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>286691</t>
+          <t>277138</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>192053</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>178322</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>203472</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>82,23%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>76,35%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>87,12%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>160382</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>149628</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>169036</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>81,11%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>75,67%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>85,49%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>194374</t>
+          <t>165569</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>179550</t>
+          <t>154456</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>206090</t>
+          <t>175509</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,17 +7668,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>354756</t>
+          <t>357622</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>338488</t>
+          <t>341421</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>371500</t>
+          <t>374088</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,32%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>41497</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>30078</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>55228</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>17,77%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>12,88%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>23,65%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>37355</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>28701</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>48109</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>18,89%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>14,51%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>24,33%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>42834</t>
+          <t>39347</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>31118</t>
+          <t>29407</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>57658</t>
+          <t>50460</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,17 +7781,17 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>80189</t>
+          <t>80844</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>63445</t>
+          <t>64378</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>96457</t>
+          <t>97045</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,13%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>233550</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>233550</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>233550</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>277</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>197737</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>197737</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>197737</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>237208</t>
+          <t>204916</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>237208</t>
+          <t>204916</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>237208</t>
+          <t>204916</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>434945</t>
+          <t>438466</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>434945</t>
+          <t>438466</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>434945</t>
+          <t>438466</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>473</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>380658</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>362215</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>394644</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>82,56%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>78,56%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>85,59%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>460</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>319866</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>304341</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>332207</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>81,67%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>77,71%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>84,83%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>473</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>399272</t>
+          <t>324410</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>381145</t>
+          <t>310839</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>414784</t>
+          <t>337298</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>719137</t>
+          <t>705067</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>696742</t>
+          <t>684521</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>739765</t>
+          <t>725196</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,58%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>80437</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>66451</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>98880</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>17,44%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>14,41%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>21,44%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>71767</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>59426</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>87292</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>18,33%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>15,17%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>22,29%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>85172</t>
+          <t>71868</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>69660</t>
+          <t>58980</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>103299</t>
+          <t>85439</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>156939</t>
+          <t>152305</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>136311</t>
+          <t>132176</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>179334</t>
+          <t>172851</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,16%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>554</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
